--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalesTransactionMaintenanceRegist.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalesTransactionMaintenanceRegist.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\桂林产品化单信披3.0.6\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>*提供销售结算资金服务机构代码</t>
   </si>
@@ -646,6 +646,10 @@
   </si>
   <si>
     <t>99 其他</t>
+  </si>
+  <si>
+    <t>*销售结算交易类型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1152,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="30.75" style="10" customWidth="1"/>
@@ -1160,19 +1164,19 @@
     <col min="3" max="3" width="17.25" style="10" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="10" customWidth="1"/>
     <col min="5" max="5" width="24.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="10" customWidth="1"/>
-    <col min="8" max="8" width="32.875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="39.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="37" style="10" customWidth="1"/>
-    <col min="11" max="11" width="22.5" customWidth="1"/>
-    <col min="12" max="13" width="22.5" style="10" customWidth="1"/>
-    <col min="14" max="14" width="27.625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="25.375" style="10" customWidth="1"/>
-    <col min="16" max="16" width="13.375" style="10" customWidth="1"/>
+    <col min="6" max="7" width="21.125" customWidth="1"/>
+    <col min="8" max="8" width="28.75" style="10" customWidth="1"/>
+    <col min="9" max="9" width="32.875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="37" style="10" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="14" width="22.5" style="10" customWidth="1"/>
+    <col min="15" max="15" width="27.625" style="10" customWidth="1"/>
+    <col min="16" max="16" width="25.375" style="10" customWidth="1"/>
+    <col min="17" max="17" width="13.375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1191,45 +1195,49 @@
       <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="L1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.15">
       <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 K1"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="例如，该笔交易在2月2日8:30:02交易成功，则交易时间为083002" sqref="N2:N1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 F1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="例如，该笔交易在2月2日8:30:02交易成功，则交易时间为083002" sqref="O2:O1048576"/>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1240,7 +1248,7 @@
           <x14:formula1>
             <xm:f>各要素值域输入规则!$A$2:$A$181</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K1048576</xm:sqref>
+          <xm:sqref>L2:L1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
